--- a/files/STable-2 .xlsx
+++ b/files/STable-2 .xlsx
@@ -562,7 +562,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="O2">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
       <c r="P2">
         <v>7.9</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>144.7</v>
+        <v>144.71</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -690,7 +690,7 @@
         <v>94.11</v>
       </c>
       <c r="O3">
-        <v>13.95</v>
+        <v>13.94</v>
       </c>
       <c r="P3">
         <v>8.890000000000001</v>
@@ -818,7 +818,7 @@
         <v>67.48999999999999</v>
       </c>
       <c r="O4">
-        <v>11.41</v>
+        <v>11.42</v>
       </c>
       <c r="P4">
         <v>8.630000000000001</v>
@@ -916,7 +916,7 @@
         <v>7.63</v>
       </c>
       <c r="E5">
-        <v>43.28</v>
+        <v>43.29</v>
       </c>
       <c r="F5">
         <v>10.12</v>
@@ -946,7 +946,7 @@
         <v>60.92</v>
       </c>
       <c r="O5">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="P5">
         <v>7.32</v>
@@ -1074,7 +1074,7 @@
         <v>77.88</v>
       </c>
       <c r="O6">
-        <v>16.72</v>
+        <v>16.7</v>
       </c>
       <c r="P6">
         <v>6.3</v>
@@ -1172,7 +1172,7 @@
         <v>10.3</v>
       </c>
       <c r="E7">
-        <v>48.94</v>
+        <v>48.93</v>
       </c>
       <c r="F7">
         <v>12.4</v>
@@ -1205,7 +1205,7 @@
         <v>12.19</v>
       </c>
       <c r="P7">
-        <v>7.59</v>
+        <v>7.6</v>
       </c>
       <c r="Q7">
         <v>271.69</v>
@@ -1330,7 +1330,7 @@
         <v>127.62</v>
       </c>
       <c r="O8">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="P8">
         <v>10.28</v>
@@ -1586,7 +1586,7 @@
         <v>108.18</v>
       </c>
       <c r="O10">
-        <v>13.29</v>
+        <v>13.3</v>
       </c>
       <c r="P10">
         <v>9.81</v>
@@ -1714,7 +1714,7 @@
         <v>86.12</v>
       </c>
       <c r="O11">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="P11">
         <v>6.45</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>195.96</v>
+        <v>195.97</v>
       </c>
       <c r="C12">
         <v>230</v>
@@ -1812,7 +1812,7 @@
         <v>6.87</v>
       </c>
       <c r="E12">
-        <v>52.09</v>
+        <v>52.08</v>
       </c>
       <c r="F12">
         <v>8.289999999999999</v>
@@ -1842,7 +1842,7 @@
         <v>109.18</v>
       </c>
       <c r="O12">
-        <v>14.27</v>
+        <v>14.26</v>
       </c>
       <c r="P12">
         <v>10.42</v>
@@ -1970,7 +1970,7 @@
         <v>124.24</v>
       </c>
       <c r="O13">
-        <v>18.85</v>
+        <v>18.86</v>
       </c>
       <c r="P13">
         <v>8.66</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>162.01</v>
+        <v>162</v>
       </c>
       <c r="C14">
         <v>248</v>
@@ -2098,7 +2098,7 @@
         <v>150.25</v>
       </c>
       <c r="O14">
-        <v>21.57</v>
+        <v>21.55</v>
       </c>
       <c r="P14">
         <v>8.67</v>
@@ -2226,7 +2226,7 @@
         <v>21.67</v>
       </c>
       <c r="O15">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="P15">
         <v>4.56</v>
@@ -2354,7 +2354,7 @@
         <v>112.07</v>
       </c>
       <c r="O16">
-        <v>17.23</v>
+        <v>17.24</v>
       </c>
       <c r="P16">
         <v>8.27</v>
@@ -2482,7 +2482,7 @@
         <v>25.25</v>
       </c>
       <c r="O17">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="P17">
         <v>5.35</v>
@@ -2610,7 +2610,7 @@
         <v>83.7</v>
       </c>
       <c r="O18">
-        <v>15.03</v>
+        <v>15.04</v>
       </c>
       <c r="P18">
         <v>7.9</v>
@@ -2738,7 +2738,7 @@
         <v>114.35</v>
       </c>
       <c r="O19">
-        <v>14.59</v>
+        <v>14.58</v>
       </c>
       <c r="P19">
         <v>10.55</v>
@@ -2866,7 +2866,7 @@
         <v>92.43000000000001</v>
       </c>
       <c r="O20">
-        <v>15.63</v>
+        <v>15.61</v>
       </c>
       <c r="P20">
         <v>7.5</v>
@@ -3122,7 +3122,7 @@
         <v>100.28</v>
       </c>
       <c r="O22">
-        <v>17.77</v>
+        <v>17.75</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -3250,7 +3250,7 @@
         <v>98.88</v>
       </c>
       <c r="O23">
-        <v>15.87</v>
+        <v>15.88</v>
       </c>
       <c r="P23">
         <v>7.67</v>
@@ -3378,7 +3378,7 @@
         <v>94.23</v>
       </c>
       <c r="O24">
-        <v>16.04</v>
+        <v>16.02</v>
       </c>
       <c r="P24">
         <v>7.91</v>
@@ -3506,7 +3506,7 @@
         <v>86.64</v>
       </c>
       <c r="O25">
-        <v>15.53</v>
+        <v>15.54</v>
       </c>
       <c r="P25">
         <v>8.880000000000001</v>
@@ -3634,7 +3634,7 @@
         <v>97.88</v>
       </c>
       <c r="O26">
-        <v>16.06</v>
+        <v>16.07</v>
       </c>
       <c r="P26">
         <v>7.99</v>
@@ -3762,7 +3762,7 @@
         <v>130.4</v>
       </c>
       <c r="O27">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="P27">
         <v>8.130000000000001</v>
@@ -3975,59 +3975,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="B29">
-        <v>182.9</v>
+        <v>85.36</v>
       </c>
       <c r="C29">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="D29">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="E29">
-        <v>40.09</v>
+        <v>40.83</v>
       </c>
       <c r="F29">
-        <v>12.07</v>
+        <v>9.07</v>
       </c>
       <c r="G29">
-        <v>78.02</v>
+        <v>79</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I29">
-        <v>17.05</v>
+        <v>14.89</v>
       </c>
       <c r="J29">
-        <v>32.33</v>
+        <v>58.61</v>
       </c>
       <c r="K29">
-        <v>188.16</v>
+        <v>161.89</v>
       </c>
       <c r="L29">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>13.3</v>
+        <v>14.12</v>
       </c>
       <c r="N29">
-        <v>114.53</v>
+        <v>81.5</v>
       </c>
       <c r="O29">
-        <v>15.42</v>
+        <v>17.66</v>
       </c>
       <c r="P29">
-        <v>8.34</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>164.56</v>
+        <v>196.75</v>
       </c>
       <c r="R29">
-        <v>48.57</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate bush</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4056,27 +4056,27 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Dark purple</t>
+          <t>Yellow with purple pigment</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Morado oscuro</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4096,75 +4096,75 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="B30">
-        <v>85.36</v>
+        <v>225.21</v>
       </c>
       <c r="C30">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="D30">
-        <v>9.4</v>
+        <v>19.33</v>
       </c>
       <c r="E30">
-        <v>40.83</v>
+        <v>37.97</v>
       </c>
       <c r="F30">
-        <v>9.07</v>
+        <v>26.07</v>
       </c>
       <c r="G30">
-        <v>79</v>
+        <v>114.1</v>
       </c>
       <c r="H30">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="I30">
-        <v>14.89</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J30">
-        <v>58.61</v>
+        <v>322.52</v>
       </c>
       <c r="K30">
-        <v>161.89</v>
+        <v>238.79</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M30">
-        <v>14.12</v>
+        <v>16.14</v>
       </c>
       <c r="N30">
-        <v>81.5</v>
+        <v>64.42</v>
       </c>
       <c r="O30">
-        <v>17.65</v>
+        <v>13.42</v>
       </c>
       <c r="P30">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="Q30">
-        <v>196.75</v>
+        <v>512.12</v>
       </c>
       <c r="R30">
-        <v>69.56999999999999</v>
+        <v>21.57</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Indeterminate bush</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4179,111 +4179,111 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Yellow with purple pigment</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Beige</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Light lilac</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Cafe</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="B31">
-        <v>225.21</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="C31">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D31">
-        <v>19.33</v>
+        <v>42.07</v>
       </c>
       <c r="E31">
-        <v>37.97</v>
+        <v>48.89</v>
       </c>
       <c r="F31">
-        <v>26.07</v>
+        <v>10.4</v>
       </c>
       <c r="G31">
-        <v>114.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H31">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I31">
-        <v>8.859999999999999</v>
+        <v>15.27</v>
       </c>
       <c r="J31">
-        <v>322.52</v>
+        <v>250.03</v>
       </c>
       <c r="K31">
-        <v>238.79</v>
+        <v>214.79</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>16.13</v>
+        <v>14.76</v>
       </c>
       <c r="N31">
-        <v>64.42</v>
+        <v>96.41</v>
       </c>
       <c r="O31">
-        <v>13.42</v>
+        <v>15.15</v>
       </c>
       <c r="P31">
-        <v>7.18</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q31">
-        <v>512.12</v>
+        <v>1021.24</v>
       </c>
       <c r="R31">
-        <v>21.57</v>
+        <v>75.34</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -4312,17 +4312,17 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with red pigment</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Beige</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4337,85 +4337,85 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Cafe</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B32">
-        <v>95.54000000000001</v>
+        <v>165.67</v>
       </c>
       <c r="C32">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D32">
-        <v>42.07</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E32">
-        <v>48.89</v>
+        <v>49.18</v>
       </c>
       <c r="F32">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="G32">
-        <v>90.09999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="H32">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I32">
-        <v>15.27</v>
+        <v>13.73</v>
       </c>
       <c r="J32">
-        <v>250.03</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="K32">
-        <v>214.79</v>
+        <v>169.97</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="M32">
-        <v>14.76</v>
+        <v>14.15</v>
       </c>
       <c r="N32">
-        <v>96.41</v>
+        <v>70</v>
       </c>
       <c r="O32">
-        <v>15.15</v>
+        <v>12.73</v>
       </c>
       <c r="P32">
-        <v>8.279999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="Q32">
-        <v>1021.24</v>
+        <v>211.8</v>
       </c>
       <c r="R32">
-        <v>75.34</v>
+        <v>43.34</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4430,17 +4430,17 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Yellow with red pigment</t>
+          <t>Pale yellow with mottling or stripes</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4465,81 +4465,81 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Grey</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="B33">
-        <v>165.67</v>
+        <v>48.01</v>
       </c>
       <c r="C33">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="D33">
-        <v>8.470000000000001</v>
+        <v>11.43</v>
       </c>
       <c r="E33">
-        <v>49.18</v>
+        <v>45.13</v>
       </c>
       <c r="F33">
-        <v>17.4</v>
+        <v>6.68</v>
       </c>
       <c r="G33">
-        <v>80.04000000000001</v>
+        <v>83</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>15.98</v>
       </c>
       <c r="I33">
-        <v>13.73</v>
+        <v>10.24</v>
       </c>
       <c r="J33">
-        <v>74.23999999999999</v>
+        <v>37.29</v>
       </c>
       <c r="K33">
-        <v>169.97</v>
+        <v>184.05</v>
       </c>
       <c r="L33">
-        <v>6.01</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>14.15</v>
+        <v>9.58</v>
       </c>
       <c r="N33">
-        <v>70</v>
+        <v>107.96</v>
       </c>
       <c r="O33">
-        <v>12.74</v>
+        <v>19.23</v>
       </c>
       <c r="P33">
-        <v>7.93</v>
+        <v>7.57</v>
       </c>
       <c r="Q33">
-        <v>211.8</v>
+        <v>17.78</v>
       </c>
       <c r="R33">
-        <v>43.34</v>
+        <v>32.7</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate bush</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4598,76 +4598,76 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B34">
-        <v>48.02</v>
+        <v>160.1</v>
       </c>
       <c r="C34">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="D34">
-        <v>11.43</v>
+        <v>7.57</v>
       </c>
       <c r="E34">
-        <v>45.13</v>
+        <v>52.21</v>
       </c>
       <c r="F34">
-        <v>6.68</v>
+        <v>10.68</v>
       </c>
       <c r="G34">
-        <v>83</v>
+        <v>81.83</v>
       </c>
       <c r="H34">
-        <v>15.98</v>
+        <v>17.98</v>
       </c>
       <c r="I34">
-        <v>10.24</v>
+        <v>14.31</v>
       </c>
       <c r="J34">
-        <v>37.29</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="K34">
-        <v>184.05</v>
+        <v>184.13</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>9.58</v>
+        <v>11.56</v>
       </c>
       <c r="N34">
-        <v>107.96</v>
+        <v>106.83</v>
       </c>
       <c r="O34">
-        <v>19.22</v>
+        <v>13.98</v>
       </c>
       <c r="P34">
-        <v>7.57</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Q34">
-        <v>17.78</v>
+        <v>161.07</v>
       </c>
       <c r="R34">
-        <v>32.7</v>
+        <v>30.7</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Indeterminate bush</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Pale yellow with mottling or stripes</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4731,75 +4731,75 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="B35">
-        <v>160.1</v>
+        <v>137.82</v>
       </c>
       <c r="C35">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="D35">
-        <v>7.57</v>
+        <v>8.1</v>
       </c>
       <c r="E35">
-        <v>52.21</v>
+        <v>51.06</v>
       </c>
       <c r="F35">
-        <v>10.68</v>
+        <v>9.68</v>
       </c>
       <c r="G35">
-        <v>81.83</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H35">
         <v>17.98</v>
       </c>
       <c r="I35">
-        <v>14.31</v>
+        <v>10.66</v>
       </c>
       <c r="J35">
-        <v>97.51000000000001</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="K35">
-        <v>184.13</v>
+        <v>211.79</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35">
-        <v>11.56</v>
+        <v>12.38</v>
       </c>
       <c r="N35">
-        <v>106.83</v>
+        <v>103.98</v>
       </c>
       <c r="O35">
-        <v>14</v>
+        <v>13.16</v>
       </c>
       <c r="P35">
-        <v>8.970000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="Q35">
-        <v>161.07</v>
+        <v>222.8</v>
       </c>
       <c r="R35">
-        <v>30.7</v>
+        <v>40.7</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4819,12 +4819,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Pale red stripe on green</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow with mottling or stripes</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4849,17 +4849,17 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4871,59 +4871,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="B36">
-        <v>137.82</v>
+        <v>146.84</v>
       </c>
       <c r="C36">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D36">
-        <v>8.1</v>
+        <v>11.67</v>
       </c>
       <c r="E36">
-        <v>51.06</v>
+        <v>40.85</v>
       </c>
       <c r="F36">
-        <v>9.68</v>
+        <v>7.73</v>
       </c>
       <c r="G36">
-        <v>82.09999999999999</v>
+        <v>118.1</v>
       </c>
       <c r="H36">
-        <v>17.98</v>
+        <v>20</v>
       </c>
       <c r="I36">
-        <v>10.66</v>
+        <v>15.04</v>
       </c>
       <c r="J36">
-        <v>79.31999999999999</v>
+        <v>141.86</v>
       </c>
       <c r="K36">
-        <v>211.79</v>
+        <v>224.79</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
       <c r="M36">
-        <v>12.38</v>
+        <v>15.42</v>
       </c>
       <c r="N36">
-        <v>103.98</v>
+        <v>99.13</v>
       </c>
       <c r="O36">
-        <v>13.16</v>
+        <v>16.59</v>
       </c>
       <c r="P36">
-        <v>9.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q36">
-        <v>222.8</v>
+        <v>486.54</v>
       </c>
       <c r="R36">
-        <v>40.7</v>
+        <v>43.19</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Pale red stripe on green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4957,37 +4957,37 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4999,63 +4999,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="B37">
-        <v>146.84</v>
+        <v>147.97</v>
       </c>
       <c r="C37">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D37">
-        <v>11.67</v>
+        <v>7.37</v>
       </c>
       <c r="E37">
-        <v>40.85</v>
+        <v>50.54</v>
       </c>
       <c r="F37">
         <v>7.73</v>
       </c>
       <c r="G37">
-        <v>118.1</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I37">
-        <v>15.04</v>
+        <v>12.79</v>
       </c>
       <c r="J37">
-        <v>141.86</v>
+        <v>139.07</v>
       </c>
       <c r="K37">
-        <v>224.79</v>
+        <v>212.97</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>4.01</v>
       </c>
       <c r="M37">
-        <v>15.42</v>
+        <v>16.44</v>
       </c>
       <c r="N37">
-        <v>99.13</v>
+        <v>93.38</v>
       </c>
       <c r="O37">
-        <v>16.59</v>
+        <v>13.74</v>
       </c>
       <c r="P37">
-        <v>8.050000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="Q37">
-        <v>486.54</v>
+        <v>397.09</v>
       </c>
       <c r="R37">
-        <v>43.19</v>
+        <v>44.19</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5070,27 +5070,27 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Pale yellow with mottling or stripes</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
+          <t>Light lilac</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
           <t>Lilac</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Broad stripes</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -5127,68 +5127,68 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="B38">
-        <v>147.97</v>
+        <v>161.72</v>
       </c>
       <c r="C38">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D38">
-        <v>7.37</v>
+        <v>15.1</v>
       </c>
       <c r="E38">
-        <v>50.54</v>
+        <v>46.64</v>
       </c>
       <c r="F38">
-        <v>7.73</v>
+        <v>14.63</v>
       </c>
       <c r="G38">
-        <v>84.04000000000001</v>
+        <v>79</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I38">
-        <v>12.79</v>
+        <v>14.7</v>
       </c>
       <c r="J38">
-        <v>139.07</v>
+        <v>144.37</v>
       </c>
       <c r="K38">
-        <v>212.97</v>
+        <v>179.89</v>
       </c>
       <c r="L38">
-        <v>4.01</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>16.44</v>
+        <v>17.01</v>
       </c>
       <c r="N38">
-        <v>93.38</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="O38">
-        <v>13.75</v>
+        <v>16.52</v>
       </c>
       <c r="P38">
-        <v>9.19</v>
+        <v>5.87</v>
       </c>
       <c r="Q38">
-        <v>397.09</v>
+        <v>208.06</v>
       </c>
       <c r="R38">
-        <v>44.19</v>
+        <v>49.57</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate prostrate</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow with mottling or stripes</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Cubic</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5238,76 +5238,76 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Broad stripes</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Whitish</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="B39">
-        <v>161.72</v>
+        <v>172.52</v>
       </c>
       <c r="C39">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D39">
-        <v>15.1</v>
+        <v>8.77</v>
       </c>
       <c r="E39">
-        <v>46.64</v>
+        <v>38.03</v>
       </c>
       <c r="F39">
-        <v>14.63</v>
+        <v>8.07</v>
       </c>
       <c r="G39">
-        <v>79</v>
+        <v>82.83</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I39">
-        <v>14.7</v>
+        <v>13.48</v>
       </c>
       <c r="J39">
-        <v>144.37</v>
+        <v>68.05</v>
       </c>
       <c r="K39">
-        <v>179.89</v>
+        <v>195.13</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>17.01</v>
+        <v>16.33</v>
       </c>
       <c r="N39">
-        <v>76.29000000000001</v>
+        <v>125.58</v>
       </c>
       <c r="O39">
-        <v>16.51</v>
+        <v>14.53</v>
       </c>
       <c r="P39">
-        <v>5.87</v>
+        <v>9.85</v>
       </c>
       <c r="Q39">
-        <v>208.06</v>
+        <v>235.72</v>
       </c>
       <c r="R39">
-        <v>49.57</v>
+        <v>38.96</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5331,37 +5331,37 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Pale yellow with mottling or stripes</t>
+          <t>Dark purple</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -5371,71 +5371,71 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="B40">
-        <v>172.52</v>
+        <v>187.66</v>
       </c>
       <c r="C40">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="D40">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E40">
-        <v>38.02</v>
+        <v>45.75</v>
       </c>
       <c r="F40">
-        <v>8.07</v>
+        <v>12.52</v>
       </c>
       <c r="G40">
-        <v>82.83</v>
+        <v>78.02</v>
       </c>
       <c r="H40">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I40">
-        <v>13.48</v>
+        <v>15.04</v>
       </c>
       <c r="J40">
-        <v>68.05</v>
+        <v>86.47</v>
       </c>
       <c r="K40">
-        <v>195.13</v>
+        <v>171.16</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>7.99</v>
       </c>
       <c r="M40">
-        <v>16.33</v>
+        <v>17.67</v>
       </c>
       <c r="N40">
-        <v>125.58</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="O40">
-        <v>14.55</v>
+        <v>14.05</v>
       </c>
       <c r="P40">
-        <v>9.85</v>
+        <v>7.13</v>
       </c>
       <c r="Q40">
-        <v>235.72</v>
+        <v>270.71</v>
       </c>
       <c r="R40">
-        <v>38.96</v>
+        <v>55.88</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -5454,120 +5454,120 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Dark purple</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
+          <t>Light lilac</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
           <t>Lilac</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="B41">
-        <v>187.67</v>
+        <v>192.13</v>
       </c>
       <c r="C41">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="D41">
-        <v>8.699999999999999</v>
+        <v>10.37</v>
       </c>
       <c r="E41">
-        <v>45.75</v>
+        <v>52.99</v>
       </c>
       <c r="F41">
-        <v>12.52</v>
+        <v>15.52</v>
       </c>
       <c r="G41">
-        <v>78.02</v>
+        <v>82</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I41">
-        <v>15.04</v>
+        <v>16.2</v>
       </c>
       <c r="J41">
-        <v>86.47</v>
+        <v>127.75</v>
       </c>
       <c r="K41">
-        <v>171.16</v>
+        <v>183.89</v>
       </c>
       <c r="L41">
-        <v>7.99</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>17.67</v>
+        <v>18.16</v>
       </c>
       <c r="N41">
-        <v>67.56999999999999</v>
+        <v>123.6</v>
       </c>
       <c r="O41">
-        <v>14.05</v>
+        <v>17.35</v>
       </c>
       <c r="P41">
-        <v>7.13</v>
+        <v>9.16</v>
       </c>
       <c r="Q41">
-        <v>270.71</v>
+        <v>538.9</v>
       </c>
       <c r="R41">
-        <v>55.88</v>
+        <v>41.88</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5582,17 +5582,17 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Dark purple</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Rhomboid mottling</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5639,187 +5639,187 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="B42">
-        <v>192.13</v>
+        <v>159.26</v>
       </c>
       <c r="C42">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D42">
-        <v>10.37</v>
+        <v>8.83</v>
       </c>
       <c r="E42">
-        <v>52.99</v>
+        <v>44.52</v>
       </c>
       <c r="F42">
-        <v>15.52</v>
+        <v>9.52</v>
       </c>
       <c r="G42">
-        <v>82</v>
+        <v>81.83</v>
       </c>
       <c r="H42">
         <v>16</v>
       </c>
       <c r="I42">
-        <v>16.2</v>
+        <v>15.91</v>
       </c>
       <c r="J42">
-        <v>127.75</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K42">
-        <v>183.89</v>
+        <v>179.13</v>
       </c>
       <c r="L42">
         <v>6</v>
       </c>
       <c r="M42">
-        <v>18.16</v>
+        <v>16.99</v>
       </c>
       <c r="N42">
-        <v>123.6</v>
+        <v>88.33</v>
       </c>
       <c r="O42">
-        <v>17.34</v>
+        <v>14.96</v>
       </c>
       <c r="P42">
-        <v>9.16</v>
+        <v>9.08</v>
       </c>
       <c r="Q42">
-        <v>538.9</v>
+        <v>219.54</v>
       </c>
       <c r="R42">
         <v>41.88</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Indeterminate climbing</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Combination 1–2–3</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Slightly curved</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Purple stripe on green</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Yellow with purple pigment</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Cream with purple pigment</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Oval</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Indeterminate climbing</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Combination 1–2–3</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Slightly curved</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Purple stripe on green</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Dark purple</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Cream with purple pigment</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Oval</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>Lilac</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Rhomboid mottling</t>
+          <t>Bicoloured mottled</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Whitish</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B43">
-        <v>159.26</v>
+        <v>140.21</v>
       </c>
       <c r="C43">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="D43">
-        <v>8.83</v>
+        <v>12.43</v>
       </c>
       <c r="E43">
-        <v>44.52</v>
+        <v>42.3</v>
       </c>
       <c r="F43">
-        <v>9.52</v>
+        <v>11.74</v>
       </c>
       <c r="G43">
-        <v>81.83</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H43">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I43">
-        <v>15.91</v>
+        <v>14.7</v>
       </c>
       <c r="J43">
-        <v>69.84999999999999</v>
+        <v>113.44</v>
       </c>
       <c r="K43">
-        <v>179.13</v>
+        <v>211.79</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>16.99</v>
+        <v>16.72</v>
       </c>
       <c r="N43">
-        <v>88.33</v>
+        <v>120.69</v>
       </c>
       <c r="O43">
-        <v>14.98</v>
+        <v>14.71</v>
       </c>
       <c r="P43">
-        <v>9.08</v>
+        <v>9.6</v>
       </c>
       <c r="Q43">
-        <v>219.54</v>
+        <v>252.65</v>
       </c>
       <c r="R43">
-        <v>41.88</v>
+        <v>35.81</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Yellow with purple pigment</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -5858,17 +5858,17 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Light lilac</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5878,80 +5878,80 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Bicoloured mottled</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Light to dark brown</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B44">
-        <v>140.21</v>
+        <v>189.49</v>
       </c>
       <c r="C44">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D44">
-        <v>12.43</v>
+        <v>13.2</v>
       </c>
       <c r="E44">
-        <v>42.3</v>
+        <v>38.78</v>
       </c>
       <c r="F44">
-        <v>11.74</v>
+        <v>15.74</v>
       </c>
       <c r="G44">
-        <v>86.09999999999999</v>
+        <v>105.83</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I44">
-        <v>14.7</v>
+        <v>9.25</v>
       </c>
       <c r="J44">
-        <v>113.44</v>
+        <v>123.63</v>
       </c>
       <c r="K44">
-        <v>211.79</v>
+        <v>220.13</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M44">
-        <v>16.72</v>
+        <v>20.72</v>
       </c>
       <c r="N44">
-        <v>120.69</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="O44">
-        <v>14.71</v>
+        <v>14.17</v>
       </c>
       <c r="P44">
-        <v>9.6</v>
+        <v>8.01</v>
       </c>
       <c r="Q44">
-        <v>252.65</v>
+        <v>265.92</v>
       </c>
       <c r="R44">
-        <v>35.81</v>
+        <v>31.81</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5991,95 +5991,95 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Light to dark brown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="B45">
-        <v>189.49</v>
+        <v>178.9</v>
       </c>
       <c r="C45">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="D45">
-        <v>13.2</v>
+        <v>11.67</v>
       </c>
       <c r="E45">
-        <v>38.78</v>
+        <v>40.75</v>
       </c>
       <c r="F45">
-        <v>15.74</v>
+        <v>33.74</v>
       </c>
       <c r="G45">
-        <v>105.83</v>
+        <v>105.02</v>
       </c>
       <c r="H45">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I45">
-        <v>9.25</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J45">
-        <v>123.63</v>
+        <v>102.25</v>
       </c>
       <c r="K45">
-        <v>220.13</v>
+        <v>214.16</v>
       </c>
       <c r="L45">
-        <v>3</v>
+        <v>3.99</v>
       </c>
       <c r="M45">
-        <v>20.72</v>
+        <v>18.93</v>
       </c>
       <c r="N45">
-        <v>91.48999999999999</v>
+        <v>100.06</v>
       </c>
       <c r="O45">
-        <v>14.19</v>
+        <v>16.45</v>
       </c>
       <c r="P45">
-        <v>8.01</v>
+        <v>7.5</v>
       </c>
       <c r="Q45">
-        <v>265.92</v>
+        <v>207.1</v>
       </c>
       <c r="R45">
-        <v>31.81</v>
+        <v>30.81</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Pale yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -6139,71 +6139,71 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="B46">
-        <v>178.9</v>
+        <v>196.52</v>
       </c>
       <c r="C46">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="D46">
-        <v>11.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E46">
-        <v>40.75</v>
+        <v>43.94</v>
       </c>
       <c r="F46">
-        <v>33.74</v>
+        <v>12.74</v>
       </c>
       <c r="G46">
-        <v>105.02</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="H46">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I46">
-        <v>9.460000000000001</v>
+        <v>16.09</v>
       </c>
       <c r="J46">
-        <v>102.25</v>
+        <v>145.04</v>
       </c>
       <c r="K46">
-        <v>214.16</v>
+        <v>176.97</v>
       </c>
       <c r="L46">
-        <v>3.99</v>
+        <v>7.01</v>
       </c>
       <c r="M46">
-        <v>18.93</v>
+        <v>17.49</v>
       </c>
       <c r="N46">
-        <v>100.06</v>
+        <v>116.34</v>
       </c>
       <c r="O46">
-        <v>16.45</v>
+        <v>18.08</v>
       </c>
       <c r="P46">
-        <v>7.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="Q46">
-        <v>207.1</v>
+        <v>639.26</v>
       </c>
       <c r="R46">
-        <v>30.81</v>
+        <v>46.96</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Pale red stripe on green</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with red pigment</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6252,90 +6252,90 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Light lilac</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Whitish</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B47">
-        <v>196.52</v>
+        <v>195.39</v>
       </c>
       <c r="C47">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D47">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E47">
-        <v>43.94</v>
+        <v>45.08</v>
       </c>
       <c r="F47">
-        <v>12.74</v>
+        <v>11.74</v>
       </c>
       <c r="G47">
-        <v>84.04000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H47">
         <v>16</v>
       </c>
       <c r="I47">
-        <v>16.09</v>
+        <v>13.81</v>
       </c>
       <c r="J47">
-        <v>145.04</v>
+        <v>112.84</v>
       </c>
       <c r="K47">
-        <v>176.97</v>
+        <v>183.79</v>
       </c>
       <c r="L47">
-        <v>7.01</v>
+        <v>7</v>
       </c>
       <c r="M47">
-        <v>17.5</v>
+        <v>17.71</v>
       </c>
       <c r="N47">
-        <v>116.34</v>
+        <v>121.18</v>
       </c>
       <c r="O47">
-        <v>18.09</v>
+        <v>15.12</v>
       </c>
       <c r="P47">
-        <v>8.470000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q47">
-        <v>639.26</v>
+        <v>365.7</v>
       </c>
       <c r="R47">
-        <v>46.96</v>
+        <v>42.96</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Very pale green</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6385,90 +6385,90 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Constant mottling</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B48">
-        <v>195.39</v>
+        <v>13.32</v>
       </c>
       <c r="C48">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="D48">
-        <v>9.9</v>
+        <v>6.43</v>
       </c>
       <c r="E48">
-        <v>45.08</v>
+        <v>51.34</v>
       </c>
       <c r="F48">
-        <v>11.74</v>
+        <v>6.52</v>
       </c>
       <c r="G48">
-        <v>83.09999999999999</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="H48">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I48">
-        <v>13.81</v>
+        <v>11.3</v>
       </c>
       <c r="J48">
-        <v>112.84</v>
+        <v>15.46</v>
       </c>
       <c r="K48">
-        <v>183.79</v>
+        <v>148.97</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>5.01</v>
       </c>
       <c r="M48">
-        <v>17.71</v>
+        <v>11.75</v>
       </c>
       <c r="N48">
-        <v>121.18</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="O48">
-        <v>15.12</v>
+        <v>15.96</v>
       </c>
       <c r="P48">
-        <v>9.800000000000001</v>
+        <v>6.92</v>
       </c>
       <c r="Q48">
-        <v>365.7</v>
+        <v>94.59</v>
       </c>
       <c r="R48">
-        <v>42.96</v>
+        <v>41.96</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Very pale green</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Determinate bush</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6483,17 +6483,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Pale red stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Yellow with red pigment</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>All leaves fallen</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6503,100 +6503,85 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>Constant mottling</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>Red to purple</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>Whitish</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B49">
-        <v>13.32</v>
+        <v>163.2</v>
       </c>
       <c r="C49">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="D49">
-        <v>6.43</v>
+        <v>9.5</v>
       </c>
       <c r="E49">
-        <v>51.34</v>
+        <v>47.33</v>
       </c>
       <c r="F49">
-        <v>6.52</v>
+        <v>13.12</v>
       </c>
       <c r="G49">
-        <v>68.04000000000001</v>
+        <v>79</v>
       </c>
       <c r="H49">
-        <v>12</v>
+        <v>20.02</v>
       </c>
       <c r="I49">
-        <v>11.3</v>
+        <v>18.06</v>
       </c>
       <c r="J49">
-        <v>15.46</v>
+        <v>81.56</v>
       </c>
       <c r="K49">
-        <v>148.97</v>
+        <v>175.89</v>
       </c>
       <c r="L49">
-        <v>5.01</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>11.75</v>
+        <v>15.29</v>
       </c>
       <c r="N49">
-        <v>66.43000000000001</v>
+        <v>120.8</v>
       </c>
       <c r="O49">
-        <v>15.97</v>
+        <v>18.82</v>
       </c>
       <c r="P49">
-        <v>6.92</v>
+        <v>8.81</v>
       </c>
       <c r="Q49">
-        <v>94.59</v>
+        <v>270.65</v>
       </c>
       <c r="R49">
-        <v>41.96</v>
+        <v>32.13</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Determinate bush</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6606,7 +6591,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6616,12 +6601,12 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Pale yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -6631,15 +6616,30 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Cubic</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
+        <is>
+          <t>White with lilac margin</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Bicoloured mottled</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>White</t>
         </is>
@@ -6648,59 +6648,59 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="B50">
-        <v>163.2</v>
+        <v>155.25</v>
       </c>
       <c r="C50">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D50">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="E50">
-        <v>47.33</v>
+        <v>50.12</v>
       </c>
       <c r="F50">
-        <v>13.12</v>
+        <v>10.07</v>
       </c>
       <c r="G50">
         <v>79</v>
       </c>
       <c r="H50">
-        <v>20.02</v>
+        <v>20</v>
       </c>
       <c r="I50">
-        <v>18.06</v>
+        <v>10.61</v>
       </c>
       <c r="J50">
-        <v>81.56</v>
+        <v>48.87</v>
       </c>
       <c r="K50">
-        <v>175.89</v>
+        <v>171.89</v>
       </c>
       <c r="L50">
         <v>6</v>
       </c>
       <c r="M50">
-        <v>15.29</v>
+        <v>13.5</v>
       </c>
       <c r="N50">
-        <v>120.8</v>
+        <v>52.79</v>
       </c>
       <c r="O50">
-        <v>18.81</v>
+        <v>10.57</v>
       </c>
       <c r="P50">
-        <v>8.81</v>
+        <v>7.58</v>
       </c>
       <c r="Q50">
-        <v>270.65</v>
+        <v>146.52</v>
       </c>
       <c r="R50">
-        <v>32.13</v>
+        <v>45.19</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>White with lilac margin</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Bicoloured mottled</t>
+          <t>Broad stripes</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -6769,125 +6769,125 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="B51">
-        <v>155.25</v>
+        <v>129.3</v>
       </c>
       <c r="C51">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="D51">
-        <v>6.6</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="E51">
-        <v>50.12</v>
+        <v>49.36</v>
       </c>
       <c r="F51">
-        <v>10.07</v>
+        <v>11.07</v>
       </c>
       <c r="G51">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H51">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I51">
-        <v>10.61</v>
+        <v>18.37</v>
       </c>
       <c r="J51">
-        <v>48.87</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K51">
-        <v>171.89</v>
+        <v>205.05</v>
       </c>
       <c r="L51">
         <v>6</v>
       </c>
       <c r="M51">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="N51">
-        <v>52.79</v>
+        <v>120.55</v>
       </c>
       <c r="O51">
-        <v>10.56</v>
+        <v>17.58</v>
       </c>
       <c r="P51">
-        <v>7.58</v>
+        <v>8.74</v>
       </c>
       <c r="Q51">
-        <v>146.52</v>
+        <v>391.86</v>
       </c>
       <c r="R51">
-        <v>45.19</v>
+        <v>52.19</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Indeterminate prostrate</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Combination 1–2–3</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Purple stripe on green</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Dark purple</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>All leaves fallen</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Cream with purple pigment</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Reniform</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Indeterminate climbing</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Combination 1–2–3</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Slightly curved</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Normal green</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Golden yellow</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Lilac</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Broad stripes</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -6897,75 +6897,75 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Dark violet</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="B52">
-        <v>129.3</v>
+        <v>210.71</v>
       </c>
       <c r="C52">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="D52">
-        <v>8.970000000000001</v>
+        <v>8</v>
       </c>
       <c r="E52">
-        <v>49.36</v>
+        <v>45.07</v>
       </c>
       <c r="F52">
-        <v>11.07</v>
+        <v>12.29</v>
       </c>
       <c r="G52">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H52">
         <v>16</v>
       </c>
       <c r="I52">
-        <v>18.37</v>
+        <v>11.54</v>
       </c>
       <c r="J52">
-        <v>74.76000000000001</v>
+        <v>43.68</v>
       </c>
       <c r="K52">
-        <v>205.05</v>
+        <v>176.05</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
       <c r="M52">
-        <v>15.7</v>
+        <v>10.74</v>
       </c>
       <c r="N52">
-        <v>120.55</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="O52">
-        <v>17.57</v>
+        <v>14.8</v>
       </c>
       <c r="P52">
-        <v>8.74</v>
+        <v>7.46</v>
       </c>
       <c r="Q52">
-        <v>391.86</v>
+        <v>173.07</v>
       </c>
       <c r="R52">
-        <v>52.19</v>
+        <v>40.81</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6980,27 +6980,27 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Dark purple</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7015,76 +7015,76 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Grey</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Dark violet</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="B53">
-        <v>210.7</v>
+        <v>146.79</v>
       </c>
       <c r="C53">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>8.27</v>
       </c>
       <c r="E53">
-        <v>45.07</v>
+        <v>44.78</v>
       </c>
       <c r="F53">
         <v>12.29</v>
       </c>
       <c r="G53">
-        <v>82</v>
+        <v>82.83</v>
       </c>
       <c r="H53">
         <v>16</v>
       </c>
       <c r="I53">
-        <v>11.54</v>
+        <v>17.16</v>
       </c>
       <c r="J53">
-        <v>43.68</v>
+        <v>56.9</v>
       </c>
       <c r="K53">
-        <v>176.05</v>
+        <v>184.13</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M53">
-        <v>10.74</v>
+        <v>11.82</v>
       </c>
       <c r="N53">
-        <v>86.34999999999999</v>
+        <v>118.72</v>
       </c>
       <c r="O53">
-        <v>14.79</v>
+        <v>16.5</v>
       </c>
       <c r="P53">
-        <v>7.46</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="Q53">
-        <v>173.07</v>
+        <v>231.36</v>
       </c>
       <c r="R53">
-        <v>40.81</v>
+        <v>46.81</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -7103,32 +7103,32 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with purple pigment</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Cream with purple pigment</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Truncate fastigiate</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7143,76 +7143,76 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B54">
-        <v>146.79</v>
+        <v>140.51</v>
       </c>
       <c r="C54">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D54">
-        <v>8.27</v>
+        <v>7.27</v>
       </c>
       <c r="E54">
-        <v>44.78</v>
+        <v>43.07</v>
       </c>
       <c r="F54">
-        <v>12.29</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G54">
-        <v>82.83</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H54">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I54">
-        <v>17.16</v>
+        <v>14.3</v>
       </c>
       <c r="J54">
-        <v>56.9</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="K54">
-        <v>184.13</v>
+        <v>194.79</v>
       </c>
       <c r="L54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>11.82</v>
+        <v>12.5</v>
       </c>
       <c r="N54">
-        <v>118.72</v>
+        <v>92.47</v>
       </c>
       <c r="O54">
-        <v>16.52</v>
+        <v>17.25</v>
       </c>
       <c r="P54">
-        <v>8.039999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="Q54">
-        <v>231.36</v>
+        <v>193.09</v>
       </c>
       <c r="R54">
-        <v>46.81</v>
+        <v>42.81</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -7231,17 +7231,17 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Yellow with purple pigment</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7271,80 +7271,80 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>Whitish</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="B55">
-        <v>140.51</v>
+        <v>193.52</v>
       </c>
       <c r="C55">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="D55">
-        <v>7.27</v>
+        <v>27.77</v>
       </c>
       <c r="E55">
-        <v>43.07</v>
+        <v>41.24</v>
       </c>
       <c r="F55">
-        <v>8.289999999999999</v>
+        <v>28.29</v>
       </c>
       <c r="G55">
-        <v>86.09999999999999</v>
+        <v>109.02</v>
       </c>
       <c r="H55">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I55">
-        <v>14.3</v>
+        <v>9.75</v>
       </c>
       <c r="J55">
-        <v>66.70999999999999</v>
+        <v>373.31</v>
       </c>
       <c r="K55">
-        <v>194.79</v>
+        <v>231.16</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>2.99</v>
       </c>
       <c r="M55">
-        <v>12.5</v>
+        <v>22.58</v>
       </c>
       <c r="N55">
-        <v>92.47</v>
+        <v>97.36</v>
       </c>
       <c r="O55">
-        <v>17.25</v>
+        <v>15.46</v>
       </c>
       <c r="P55">
-        <v>7.62</v>
+        <v>8.07</v>
       </c>
       <c r="Q55">
-        <v>193.09</v>
+        <v>366.63</v>
       </c>
       <c r="R55">
-        <v>42.81</v>
+        <v>19.72</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Combination 1–2–3</t>
+          <t>Combination 2–3</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with red pigment</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Truncate fastigiate</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -7416,78 +7416,78 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="B56">
-        <v>193.52</v>
+        <v>152.98</v>
       </c>
       <c r="C56">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="D56">
-        <v>27.77</v>
+        <v>5.63</v>
       </c>
       <c r="E56">
-        <v>41.24</v>
+        <v>48.71</v>
       </c>
       <c r="F56">
-        <v>28.29</v>
+        <v>18.29</v>
       </c>
       <c r="G56">
-        <v>109.02</v>
+        <v>79</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I56">
-        <v>9.75</v>
+        <v>12.2</v>
       </c>
       <c r="J56">
-        <v>373.31</v>
+        <v>36.59</v>
       </c>
       <c r="K56">
-        <v>231.16</v>
+        <v>171.89</v>
       </c>
       <c r="L56">
-        <v>2.99</v>
+        <v>6</v>
       </c>
       <c r="M56">
-        <v>22.58</v>
+        <v>13.43</v>
       </c>
       <c r="N56">
-        <v>97.36</v>
+        <v>56.1</v>
       </c>
       <c r="O56">
-        <v>15.46</v>
+        <v>12.81</v>
       </c>
       <c r="P56">
-        <v>8.07</v>
+        <v>6.79</v>
       </c>
       <c r="Q56">
-        <v>366.63</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="R56">
-        <v>19.72</v>
+        <v>52.72</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate prostrate</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Combination 2–3</t>
+          <t>Combination 1–2–3</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Yellow with red pigment</t>
+          <t>Dark purple</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>All leaves fallen</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7512,91 +7512,91 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Grey</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="B57">
-        <v>152.98</v>
+        <v>172.11</v>
       </c>
       <c r="C57">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D57">
-        <v>5.63</v>
+        <v>7.17</v>
       </c>
       <c r="E57">
-        <v>48.72</v>
+        <v>50.67</v>
       </c>
       <c r="F57">
-        <v>18.29</v>
+        <v>14.29</v>
       </c>
       <c r="G57">
-        <v>79</v>
+        <v>78.83</v>
       </c>
       <c r="H57">
         <v>18</v>
       </c>
       <c r="I57">
-        <v>12.2</v>
+        <v>15.64</v>
       </c>
       <c r="J57">
-        <v>36.59</v>
+        <v>63.69</v>
       </c>
       <c r="K57">
-        <v>171.89</v>
+        <v>172.13</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>13.43</v>
+        <v>16.5</v>
       </c>
       <c r="N57">
-        <v>56.1</v>
+        <v>50.03</v>
       </c>
       <c r="O57">
-        <v>12.8</v>
+        <v>10.84</v>
       </c>
       <c r="P57">
-        <v>6.79</v>
+        <v>7.81</v>
       </c>
       <c r="Q57">
-        <v>88.81999999999999</v>
+        <v>245.46</v>
       </c>
       <c r="R57">
-        <v>52.72</v>
+        <v>63.72</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Dark purple</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7672,59 +7672,59 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="B58">
-        <v>172.12</v>
+        <v>110.2</v>
       </c>
       <c r="C58">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D58">
-        <v>7.17</v>
+        <v>14.1</v>
       </c>
       <c r="E58">
-        <v>50.67</v>
+        <v>50.14</v>
       </c>
       <c r="F58">
-        <v>14.29</v>
+        <v>28.07</v>
       </c>
       <c r="G58">
-        <v>78.83</v>
+        <v>106</v>
       </c>
       <c r="H58">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I58">
-        <v>15.64</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J58">
-        <v>63.69</v>
+        <v>312.4</v>
       </c>
       <c r="K58">
-        <v>172.13</v>
+        <v>238.89</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>16.5</v>
+        <v>20.16</v>
       </c>
       <c r="N58">
-        <v>50.03</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O58">
-        <v>10.86</v>
+        <v>17.95</v>
       </c>
       <c r="P58">
-        <v>7.81</v>
+        <v>7.98</v>
       </c>
       <c r="Q58">
-        <v>245.46</v>
+        <v>849.84</v>
       </c>
       <c r="R58">
-        <v>63.72</v>
+        <v>29.42</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7753,32 +7753,32 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Beige</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Carmine red</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -7793,66 +7793,66 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="B59">
-        <v>110.2</v>
+        <v>151.73</v>
       </c>
       <c r="C59">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D59">
-        <v>14.1</v>
+        <v>6.47</v>
       </c>
       <c r="E59">
-        <v>50.14</v>
+        <v>51.37</v>
       </c>
       <c r="F59">
-        <v>28.07</v>
+        <v>18.07</v>
       </c>
       <c r="G59">
-        <v>106</v>
+        <v>82.02</v>
       </c>
       <c r="H59">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I59">
-        <v>9.609999999999999</v>
+        <v>15.29</v>
       </c>
       <c r="J59">
-        <v>312.4</v>
+        <v>74.13</v>
       </c>
       <c r="K59">
-        <v>238.89</v>
+        <v>171.16</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="M59">
-        <v>20.16</v>
+        <v>15.51</v>
       </c>
       <c r="N59">
-        <v>96.15000000000001</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="O59">
-        <v>17.94</v>
+        <v>16.56</v>
       </c>
       <c r="P59">
-        <v>7.98</v>
+        <v>7.03</v>
       </c>
       <c r="Q59">
-        <v>849.84</v>
+        <v>244.65</v>
       </c>
       <c r="R59">
-        <v>29.42</v>
+        <v>48.42</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -7876,12 +7876,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Pale yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Beige</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7901,17 +7901,17 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Carmine red</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -7921,63 +7921,63 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Grey</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B60">
-        <v>151.73</v>
+        <v>120.8</v>
       </c>
       <c r="C60">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D60">
-        <v>6.47</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E60">
-        <v>51.37</v>
+        <v>49.95</v>
       </c>
       <c r="F60">
-        <v>18.07</v>
+        <v>7.29</v>
       </c>
       <c r="G60">
-        <v>82.02</v>
+        <v>82</v>
       </c>
       <c r="H60">
         <v>16</v>
       </c>
       <c r="I60">
-        <v>15.29</v>
+        <v>13.31</v>
       </c>
       <c r="J60">
-        <v>74.13</v>
+        <v>43.47</v>
       </c>
       <c r="K60">
-        <v>171.16</v>
+        <v>196.05</v>
       </c>
       <c r="L60">
-        <v>5.99</v>
+        <v>7</v>
       </c>
       <c r="M60">
-        <v>15.51</v>
+        <v>14.3</v>
       </c>
       <c r="N60">
-        <v>87.20999999999999</v>
+        <v>125.79</v>
       </c>
       <c r="O60">
-        <v>16.56</v>
+        <v>14.94</v>
       </c>
       <c r="P60">
-        <v>7.03</v>
+        <v>9.99</v>
       </c>
       <c r="Q60">
-        <v>244.65</v>
+        <v>212.93</v>
       </c>
       <c r="R60">
         <v>48.42</v>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with purple pigment</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -8049,122 +8049,122 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="B61">
-        <v>120.79</v>
+        <v>140.75</v>
       </c>
       <c r="C61">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D61">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E61">
-        <v>49.95</v>
+        <v>44.17</v>
       </c>
       <c r="F61">
-        <v>7.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G61">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H61">
         <v>16</v>
       </c>
       <c r="I61">
-        <v>13.31</v>
+        <v>14.54</v>
       </c>
       <c r="J61">
-        <v>43.47</v>
+        <v>76.58</v>
       </c>
       <c r="K61">
-        <v>196.05</v>
+        <v>194.89</v>
       </c>
       <c r="L61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>14.3</v>
+        <v>15.33</v>
       </c>
       <c r="N61">
-        <v>125.79</v>
+        <v>111.48</v>
       </c>
       <c r="O61">
-        <v>14.93</v>
+        <v>14.71</v>
       </c>
       <c r="P61">
-        <v>9.99</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q61">
-        <v>212.93</v>
+        <v>283.59</v>
       </c>
       <c r="R61">
-        <v>48.42</v>
+        <v>36.42</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
+          <t>Very pale green</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Indeterminate climbing</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Combination 1–2–3</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Slightly curved</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Purple stripe on green</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Yellow with purple pigment</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Cream with purple pigment</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Indeterminate climbing</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Combination 1–2–3</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Curved</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Bright green</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Yellow with purple pigment</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>Golden yellow</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>Lilac</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Lilac</t>
-        </is>
-      </c>
       <c r="AD61" t="inlineStr">
         <is>
           <t>Striped</t>
@@ -8172,75 +8172,75 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B62">
-        <v>140.75</v>
+        <v>190.6</v>
       </c>
       <c r="C62">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D62">
-        <v>8.800000000000001</v>
+        <v>14.37</v>
       </c>
       <c r="E62">
-        <v>44.17</v>
+        <v>39.05</v>
       </c>
       <c r="F62">
-        <v>9.289999999999999</v>
+        <v>6.29</v>
       </c>
       <c r="G62">
-        <v>86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H62">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I62">
-        <v>14.54</v>
+        <v>15.33</v>
       </c>
       <c r="J62">
-        <v>76.58</v>
+        <v>177.49</v>
       </c>
       <c r="K62">
-        <v>194.89</v>
+        <v>238.79</v>
       </c>
       <c r="L62">
         <v>6</v>
       </c>
       <c r="M62">
-        <v>15.33</v>
+        <v>17.32</v>
       </c>
       <c r="N62">
-        <v>111.48</v>
+        <v>123.37</v>
       </c>
       <c r="O62">
-        <v>14.7</v>
+        <v>15.35</v>
       </c>
       <c r="P62">
-        <v>9.449999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="Q62">
-        <v>283.59</v>
+        <v>731.95</v>
       </c>
       <c r="R62">
-        <v>36.42</v>
+        <v>48.42</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Very pale green</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Combination 1–2–3</t>
+          <t>Combination 2–3</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves fallen</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -8305,66 +8305,66 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Whitish</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="B63">
-        <v>190.6</v>
+        <v>140.67</v>
       </c>
       <c r="C63">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D63">
-        <v>14.37</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E63">
-        <v>39.05</v>
+        <v>44.65</v>
       </c>
       <c r="F63">
-        <v>6.29</v>
+        <v>7.52</v>
       </c>
       <c r="G63">
-        <v>93.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H63">
-        <v>22</v>
+        <v>20.01</v>
       </c>
       <c r="I63">
-        <v>15.33</v>
+        <v>13.89</v>
       </c>
       <c r="J63">
-        <v>177.49</v>
+        <v>68.69</v>
       </c>
       <c r="K63">
-        <v>238.79</v>
+        <v>183.79</v>
       </c>
       <c r="L63">
         <v>6</v>
       </c>
       <c r="M63">
-        <v>17.32</v>
+        <v>15.75</v>
       </c>
       <c r="N63">
-        <v>123.37</v>
+        <v>124.99</v>
       </c>
       <c r="O63">
-        <v>15.35</v>
+        <v>17.24</v>
       </c>
       <c r="P63">
-        <v>10.07</v>
+        <v>9.23</v>
       </c>
       <c r="Q63">
-        <v>731.95</v>
+        <v>240.07</v>
       </c>
       <c r="R63">
-        <v>48.42</v>
+        <v>43.8</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -8378,27 +8378,27 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Combination 2–3</t>
+          <t>Combination 1–2–3</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Pale red stripe on green</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Yellow with purple pigment</t>
+          <t>Yellow with red pigment</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Truncate fastigiate</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Light lilac</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -8440,63 +8440,63 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="B64">
-        <v>140.67</v>
+        <v>134.8</v>
       </c>
       <c r="C64">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D64">
-        <v>8.529999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="E64">
-        <v>44.65</v>
+        <v>47.25</v>
       </c>
       <c r="F64">
-        <v>7.52</v>
+        <v>13.52</v>
       </c>
       <c r="G64">
-        <v>76.09999999999999</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="H64">
-        <v>20.01</v>
+        <v>16.01</v>
       </c>
       <c r="I64">
-        <v>13.89</v>
+        <v>16.03</v>
       </c>
       <c r="J64">
-        <v>68.69</v>
+        <v>56.89</v>
       </c>
       <c r="K64">
-        <v>183.79</v>
+        <v>176.97</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>7.01</v>
       </c>
       <c r="M64">
-        <v>15.75</v>
+        <v>17.81</v>
       </c>
       <c r="N64">
-        <v>124.99</v>
+        <v>127.94</v>
       </c>
       <c r="O64">
-        <v>17.24</v>
+        <v>17.72</v>
       </c>
       <c r="P64">
-        <v>9.23</v>
+        <v>9.58</v>
       </c>
       <c r="Q64">
-        <v>240.07</v>
+        <v>284.62</v>
       </c>
       <c r="R64">
-        <v>43.8</v>
+        <v>45.8</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Pale red stripe on green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Yellow with red pigment</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Cream with purple pigment</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Truncate fastigiate</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8551,208 +8551,208 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>Whitish</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="B65">
-        <v>134.8</v>
+        <v>143.95</v>
       </c>
       <c r="C65">
         <v>220</v>
       </c>
       <c r="D65">
-        <v>7.8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E65">
-        <v>47.25</v>
+        <v>45.97</v>
       </c>
       <c r="F65">
-        <v>13.52</v>
+        <v>12.52</v>
       </c>
       <c r="G65">
-        <v>84.04000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="H65">
-        <v>16.01</v>
+        <v>20.01</v>
       </c>
       <c r="I65">
-        <v>16.03</v>
+        <v>16.14</v>
       </c>
       <c r="J65">
-        <v>56.89</v>
+        <v>98.88</v>
       </c>
       <c r="K65">
-        <v>176.97</v>
+        <v>184.13</v>
       </c>
       <c r="L65">
-        <v>7.01</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>17.81</v>
+        <v>15.02</v>
       </c>
       <c r="N65">
-        <v>127.94</v>
+        <v>105.37</v>
       </c>
       <c r="O65">
-        <v>17.73</v>
+        <v>15.07</v>
       </c>
       <c r="P65">
-        <v>9.58</v>
+        <v>9.18</v>
       </c>
       <c r="Q65">
-        <v>284.62</v>
+        <v>273.33</v>
       </c>
       <c r="R65">
-        <v>45.8</v>
+        <v>30.8</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Indeterminate climbing</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Combination 1–2–3</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Slightly curved</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Purple stripe on green</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Golden yellow</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Oval</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Indeterminate climbing</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Combination 1–2–3</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Slightly curved</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Bright green</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Golden yellow</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Reniform</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Lilac</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Striped</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="B66">
-        <v>143.95</v>
+        <v>142.04</v>
       </c>
       <c r="C66">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D66">
-        <v>8.029999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="E66">
-        <v>45.97</v>
+        <v>44.3</v>
       </c>
       <c r="F66">
-        <v>12.52</v>
+        <v>14.07</v>
       </c>
       <c r="G66">
-        <v>78.83</v>
+        <v>82.02</v>
       </c>
       <c r="H66">
-        <v>20.01</v>
+        <v>16</v>
       </c>
       <c r="I66">
-        <v>16.14</v>
+        <v>14.89</v>
       </c>
       <c r="J66">
-        <v>98.88</v>
+        <v>49</v>
       </c>
       <c r="K66">
-        <v>184.13</v>
+        <v>175.16</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>6.99</v>
       </c>
       <c r="M66">
-        <v>15.02</v>
+        <v>15.1</v>
       </c>
       <c r="N66">
-        <v>105.37</v>
+        <v>123.17</v>
       </c>
       <c r="O66">
-        <v>15.09</v>
+        <v>15.81</v>
       </c>
       <c r="P66">
-        <v>9.18</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q66">
-        <v>273.33</v>
+        <v>237.59</v>
       </c>
       <c r="R66">
-        <v>30.8</v>
+        <v>48.34</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Truncate fastigiate</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -8807,100 +8807,100 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Grey</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B67">
-        <v>142.04</v>
+        <v>13.64</v>
       </c>
       <c r="C67">
-        <v>230</v>
+        <v>41</v>
       </c>
       <c r="D67">
-        <v>8.07</v>
+        <v>8.9</v>
       </c>
       <c r="E67">
-        <v>44.3</v>
+        <v>44.87</v>
       </c>
       <c r="F67">
-        <v>14.07</v>
+        <v>4.07</v>
       </c>
       <c r="G67">
-        <v>82.02</v>
+        <v>87.83</v>
       </c>
       <c r="H67">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I67">
-        <v>14.89</v>
+        <v>11.4</v>
       </c>
       <c r="J67">
-        <v>49</v>
+        <v>21.38</v>
       </c>
       <c r="K67">
-        <v>175.16</v>
+        <v>172.13</v>
       </c>
       <c r="L67">
-        <v>6.99</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>15.1</v>
+        <v>13.92</v>
       </c>
       <c r="N67">
-        <v>123.17</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="O67">
-        <v>15.81</v>
+        <v>13.51</v>
       </c>
       <c r="P67">
-        <v>9.289999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="Q67">
-        <v>237.59</v>
+        <v>64.42</v>
       </c>
       <c r="R67">
-        <v>48.34</v>
+        <v>30.34</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Very pale green</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Determinate bush</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Combination 1–2–3</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -8920,17 +8920,17 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Truncate fastigiate</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>Amarillo a verdoso</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8952,35 +8952,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B68">
-        <v>13.64</v>
+        <v>147.97</v>
       </c>
       <c r="C68">
-        <v>41</v>
+        <v>250</v>
       </c>
       <c r="D68">
-        <v>8.9</v>
+        <v>9.17</v>
       </c>
       <c r="E68">
-        <v>44.87</v>
+        <v>49.38</v>
       </c>
       <c r="F68">
-        <v>4.07</v>
+        <v>7.4</v>
       </c>
       <c r="G68">
-        <v>87.83</v>
+        <v>78.83</v>
       </c>
       <c r="H68">
-        <v>12</v>
+        <v>18.01</v>
       </c>
       <c r="I68">
-        <v>11.4</v>
+        <v>14.8</v>
       </c>
       <c r="J68">
-        <v>21.38</v>
+        <v>77.88</v>
       </c>
       <c r="K68">
         <v>172.13</v>
@@ -8989,46 +8989,46 @@
         <v>5</v>
       </c>
       <c r="M68">
-        <v>13.92</v>
+        <v>16.43</v>
       </c>
       <c r="N68">
-        <v>64.31999999999999</v>
+        <v>94.62</v>
       </c>
       <c r="O68">
-        <v>13.53</v>
+        <v>15.16</v>
       </c>
       <c r="P68">
-        <v>7.18</v>
+        <v>8.83</v>
       </c>
       <c r="Q68">
-        <v>64.42</v>
+        <v>327.53</v>
       </c>
       <c r="R68">
-        <v>30.34</v>
+        <v>35.88</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Very pale green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Determinate bush</t>
+          <t>Indeterminate prostrate</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Combination 1–2–3</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -9048,91 +9048,91 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
+          <t>Lilac</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>White with lilac veins</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
           <t>White</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>Amarillo a verdoso</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B69">
-        <v>147.97</v>
+        <v>144.89</v>
       </c>
       <c r="C69">
         <v>250</v>
       </c>
       <c r="D69">
-        <v>9.17</v>
+        <v>7.7</v>
       </c>
       <c r="E69">
-        <v>49.38</v>
+        <v>44.86</v>
       </c>
       <c r="F69">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="G69">
-        <v>78.83</v>
+        <v>79</v>
       </c>
       <c r="H69">
-        <v>18.01</v>
+        <v>20.01</v>
       </c>
       <c r="I69">
-        <v>14.8</v>
+        <v>16.55</v>
       </c>
       <c r="J69">
-        <v>77.88</v>
+        <v>82.67</v>
       </c>
       <c r="K69">
-        <v>172.13</v>
+        <v>195.05</v>
       </c>
       <c r="L69">
         <v>5</v>
       </c>
       <c r="M69">
-        <v>16.43</v>
+        <v>16.36</v>
       </c>
       <c r="N69">
-        <v>94.62</v>
+        <v>116.26</v>
       </c>
       <c r="O69">
-        <v>15.18</v>
+        <v>17.95</v>
       </c>
       <c r="P69">
-        <v>8.83</v>
+        <v>8.56</v>
       </c>
       <c r="Q69">
-        <v>327.53</v>
+        <v>244.24</v>
       </c>
       <c r="R69">
-        <v>35.88</v>
+        <v>44.88</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Cubic</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>White with lilac veins</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Striped</t>
+          <t>Broad stripes</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -9201,75 +9201,75 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B70">
-        <v>144.89</v>
+        <v>80.58</v>
       </c>
       <c r="C70">
-        <v>250</v>
+        <v>129</v>
       </c>
       <c r="D70">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="E70">
-        <v>44.86</v>
+        <v>38.26</v>
       </c>
       <c r="F70">
-        <v>9.4</v>
+        <v>7.52</v>
       </c>
       <c r="G70">
-        <v>79</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H70">
-        <v>20.01</v>
+        <v>18.01</v>
       </c>
       <c r="I70">
-        <v>16.55</v>
+        <v>12.22</v>
       </c>
       <c r="J70">
-        <v>82.67</v>
+        <v>63.46</v>
       </c>
       <c r="K70">
-        <v>195.05</v>
+        <v>175.79</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>16.36</v>
+        <v>16.19</v>
       </c>
       <c r="N70">
-        <v>116.26</v>
+        <v>87.22</v>
       </c>
       <c r="O70">
-        <v>17.94</v>
+        <v>12.72</v>
       </c>
       <c r="P70">
-        <v>8.56</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q70">
-        <v>244.24</v>
+        <v>148.35</v>
       </c>
       <c r="R70">
-        <v>44.88</v>
+        <v>46.57</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate prostrate</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Pale yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9304,91 +9304,91 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Broad stripes</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blanco puro</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B71">
-        <v>80.58</v>
+        <v>131.55</v>
       </c>
       <c r="C71">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="D71">
-        <v>7.67</v>
+        <v>6</v>
       </c>
       <c r="E71">
-        <v>38.26</v>
+        <v>44.86</v>
       </c>
       <c r="F71">
-        <v>7.52</v>
+        <v>10.29</v>
       </c>
       <c r="G71">
-        <v>73.09999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="H71">
-        <v>18.01</v>
+        <v>17.9</v>
       </c>
       <c r="I71">
-        <v>12.22</v>
+        <v>17.38</v>
       </c>
       <c r="J71">
-        <v>63.46</v>
+        <v>50.87</v>
       </c>
       <c r="K71">
-        <v>175.79</v>
+        <v>176.97</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6.01</v>
       </c>
       <c r="M71">
-        <v>16.19</v>
+        <v>20.35</v>
       </c>
       <c r="N71">
-        <v>87.22</v>
+        <v>67.16</v>
       </c>
       <c r="O71">
-        <v>12.72</v>
+        <v>14.34</v>
       </c>
       <c r="P71">
-        <v>9.390000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="Q71">
-        <v>148.35</v>
+        <v>135.71</v>
       </c>
       <c r="R71">
-        <v>46.57</v>
+        <v>50.57</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -9447,80 +9447,80 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>Blanco puro</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B72">
-        <v>131.55</v>
+        <v>150.42</v>
       </c>
       <c r="C72">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>6.23</v>
       </c>
       <c r="E72">
-        <v>44.86</v>
+        <v>38.13</v>
       </c>
       <c r="F72">
-        <v>10.29</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G72">
-        <v>74.04000000000001</v>
+        <v>79</v>
       </c>
       <c r="H72">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="I72">
-        <v>17.38</v>
+        <v>12.27</v>
       </c>
       <c r="J72">
-        <v>50.87</v>
+        <v>25.4</v>
       </c>
       <c r="K72">
-        <v>176.97</v>
+        <v>172.05</v>
       </c>
       <c r="L72">
-        <v>6.01</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>20.35</v>
+        <v>13.44</v>
       </c>
       <c r="N72">
-        <v>67.16</v>
+        <v>63.38</v>
       </c>
       <c r="O72">
-        <v>14.35</v>
+        <v>11.52</v>
       </c>
       <c r="P72">
-        <v>7.35</v>
+        <v>7.51</v>
       </c>
       <c r="Q72">
-        <v>135.71</v>
+        <v>56.69</v>
       </c>
       <c r="R72">
-        <v>50.57</v>
+        <v>62.8</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>All leaves fallen</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9560,95 +9560,95 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Cubic</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Light to dark brown</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B73">
-        <v>150.42</v>
+        <v>211.31</v>
       </c>
       <c r="C73">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="D73">
-        <v>6.23</v>
+        <v>21.97</v>
       </c>
       <c r="E73">
-        <v>38.13</v>
+        <v>41.8</v>
       </c>
       <c r="F73">
-        <v>8.630000000000001</v>
+        <v>17.85</v>
       </c>
       <c r="G73">
-        <v>79</v>
+        <v>115.04</v>
       </c>
       <c r="H73">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I73">
-        <v>12.27</v>
+        <v>12.17</v>
       </c>
       <c r="J73">
-        <v>25.4</v>
+        <v>97.16</v>
       </c>
       <c r="K73">
-        <v>172.05</v>
+        <v>222.97</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>3.01</v>
       </c>
       <c r="M73">
-        <v>13.44</v>
+        <v>22.22</v>
       </c>
       <c r="N73">
-        <v>63.38</v>
+        <v>95.77</v>
       </c>
       <c r="O73">
-        <v>11.51</v>
+        <v>14.91</v>
       </c>
       <c r="P73">
-        <v>7.51</v>
+        <v>8.75</v>
       </c>
       <c r="Q73">
-        <v>56.69</v>
+        <v>188.67</v>
       </c>
       <c r="R73">
-        <v>62.8</v>
+        <v>29.96</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Very pale green</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Pale yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>All leaves fallen</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -9688,91 +9688,91 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>White</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Constant mottling</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>Light to dark brown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B74">
-        <v>211.31</v>
+        <v>122.2</v>
       </c>
       <c r="C74">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="D74">
-        <v>21.97</v>
+        <v>11.27</v>
       </c>
       <c r="E74">
-        <v>41.8</v>
+        <v>43.19</v>
       </c>
       <c r="F74">
-        <v>17.85</v>
+        <v>8.07</v>
       </c>
       <c r="G74">
-        <v>115.04</v>
+        <v>83</v>
       </c>
       <c r="H74">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I74">
-        <v>12.17</v>
+        <v>15.2</v>
       </c>
       <c r="J74">
-        <v>97.16</v>
+        <v>68.22</v>
       </c>
       <c r="K74">
-        <v>222.97</v>
+        <v>195.89</v>
       </c>
       <c r="L74">
-        <v>3.01</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>22.22</v>
+        <v>16.34</v>
       </c>
       <c r="N74">
-        <v>95.77</v>
+        <v>93.91</v>
       </c>
       <c r="O74">
-        <v>14.92</v>
+        <v>13.84</v>
       </c>
       <c r="P74">
-        <v>8.75</v>
+        <v>8.49</v>
       </c>
       <c r="Q74">
-        <v>188.67</v>
+        <v>227.16</v>
       </c>
       <c r="R74">
-        <v>29.96</v>
+        <v>38.65</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -9791,12 +9791,12 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Bright green</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -9806,110 +9806,110 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Pale yellow to white</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Light lilac</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Constant mottling</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="B75">
-        <v>122.2</v>
+        <v>127.55</v>
       </c>
       <c r="C75">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="D75">
-        <v>11.27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E75">
-        <v>43.19</v>
+        <v>43.04</v>
       </c>
       <c r="F75">
-        <v>8.07</v>
+        <v>13.07</v>
       </c>
       <c r="G75">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H75">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="I75">
-        <v>15.2</v>
+        <v>14.41</v>
       </c>
       <c r="J75">
-        <v>68.22</v>
+        <v>37.32</v>
       </c>
       <c r="K75">
-        <v>195.89</v>
+        <v>183.79</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
       <c r="M75">
-        <v>16.34</v>
+        <v>15.59</v>
       </c>
       <c r="N75">
-        <v>93.91</v>
+        <v>113.07</v>
       </c>
       <c r="O75">
-        <v>13.83</v>
+        <v>19.7</v>
       </c>
       <c r="P75">
-        <v>8.49</v>
+        <v>8.43</v>
       </c>
       <c r="Q75">
-        <v>227.16</v>
+        <v>117.83</v>
       </c>
       <c r="R75">
-        <v>38.65</v>
+        <v>37.72</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Very pale green</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Indeterminate climbing</t>
+          <t>Indeterminate prostrate</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Bright green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -9934,110 +9934,110 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>Pale yellow to white</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Cubic</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>White with lilac margin</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Bicoloured mottled</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B76">
-        <v>127.55</v>
+        <v>151.68</v>
       </c>
       <c r="C76">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D76">
-        <v>8.300000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="E76">
-        <v>43.04</v>
+        <v>44.94</v>
       </c>
       <c r="F76">
-        <v>13.07</v>
+        <v>11.07</v>
       </c>
       <c r="G76">
-        <v>83.09999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="H76">
-        <v>16.01</v>
+        <v>20.01</v>
       </c>
       <c r="I76">
-        <v>14.41</v>
+        <v>15.29</v>
       </c>
       <c r="J76">
-        <v>37.32</v>
+        <v>50.52</v>
       </c>
       <c r="K76">
-        <v>183.79</v>
+        <v>196.97</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="M76">
-        <v>15.59</v>
+        <v>18.61</v>
       </c>
       <c r="N76">
-        <v>113.07</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O76">
-        <v>19.7</v>
+        <v>13.25</v>
       </c>
       <c r="P76">
-        <v>8.43</v>
+        <v>10.5</v>
       </c>
       <c r="Q76">
-        <v>117.83</v>
+        <v>183.39</v>
       </c>
       <c r="R76">
-        <v>37.72</v>
+        <v>46.72</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Very pale green</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Indeterminate prostrate</t>
+          <t>Indeterminate climbing</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10047,120 +10047,120 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Curved</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Purple stripe on green</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow with purple pigment</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Golden yellow</t>
+          <t>Morado oscuro</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
+          <t>Light lilac</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
           <t>Lilac</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>White with lilac margin</t>
-        </is>
-      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Bicoloured mottled</t>
+          <t>Mottled</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B77">
-        <v>151.68</v>
+        <v>178.83</v>
       </c>
       <c r="C77">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D77">
-        <v>6.53</v>
+        <v>10.03</v>
       </c>
       <c r="E77">
-        <v>44.94</v>
+        <v>40.13</v>
       </c>
       <c r="F77">
-        <v>11.07</v>
+        <v>7.07</v>
       </c>
       <c r="G77">
-        <v>80.04000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="H77">
-        <v>20.01</v>
+        <v>16.01</v>
       </c>
       <c r="I77">
-        <v>15.29</v>
+        <v>15.28</v>
       </c>
       <c r="J77">
-        <v>50.52</v>
+        <v>47.51</v>
       </c>
       <c r="K77">
-        <v>196.97</v>
+        <v>196.13</v>
       </c>
       <c r="L77">
-        <v>6.01</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>18.61</v>
+        <v>14.73</v>
       </c>
       <c r="N77">
-        <v>98.81999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="O77">
-        <v>13.26</v>
+        <v>14.92</v>
       </c>
       <c r="P77">
-        <v>10.5</v>
+        <v>7.12</v>
       </c>
       <c r="Q77">
-        <v>183.39</v>
+        <v>186.1</v>
       </c>
       <c r="R77">
-        <v>46.72</v>
+        <v>75.72</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Very pale green</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -10175,32 +10175,32 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>Slightly curved</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Purple stripe on green</t>
+          <t>Normal green</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Yellow with purple pigment</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>All leaves persistent</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Morado oscuro</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -10215,80 +10215,80 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Mottled</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Red to purple</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>Light coffee brown</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B78">
-        <v>178.83</v>
+        <v>185.65</v>
       </c>
       <c r="C78">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="D78">
-        <v>10.03</v>
+        <v>9.1</v>
       </c>
       <c r="E78">
-        <v>40.13</v>
+        <v>43.52</v>
       </c>
       <c r="F78">
-        <v>7.07</v>
+        <v>11.08</v>
       </c>
       <c r="G78">
-        <v>81.83</v>
+        <v>79</v>
       </c>
       <c r="H78">
-        <v>16.01</v>
+        <v>18.01</v>
       </c>
       <c r="I78">
-        <v>15.28</v>
+        <v>15.24</v>
       </c>
       <c r="J78">
-        <v>47.51</v>
+        <v>58.53</v>
       </c>
       <c r="K78">
-        <v>196.13</v>
+        <v>179.05</v>
       </c>
       <c r="L78">
         <v>7</v>
       </c>
       <c r="M78">
-        <v>14.73</v>
+        <v>11.74</v>
       </c>
       <c r="N78">
-        <v>79.48999999999999</v>
+        <v>79.23</v>
       </c>
       <c r="O78">
-        <v>14.94</v>
+        <v>13.55</v>
       </c>
       <c r="P78">
-        <v>7.12</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q78">
-        <v>186.1</v>
+        <v>203.38</v>
       </c>
       <c r="R78">
-        <v>75.72</v>
+        <v>48.76</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Normal green</t>
+          <t>Pale red stripe on green</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Pale yellow</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>All leaves persistent</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -10328,17 +10328,17 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Reniform</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Light lilac</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Lila oscuro con manchas violA!cias</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>Red to purple</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -10360,129 +10360,59 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>CHECKS</t>
         </is>
       </c>
       <c r="B79">
-        <v>185.65</v>
+        <v>82.05</v>
       </c>
       <c r="C79">
-        <v>230</v>
+        <v>139.47</v>
       </c>
       <c r="D79">
-        <v>9.1</v>
+        <v>8.17</v>
       </c>
       <c r="E79">
-        <v>43.52</v>
+        <v>47.13</v>
       </c>
       <c r="F79">
-        <v>11.08</v>
+        <v>8.16</v>
       </c>
       <c r="G79">
-        <v>79</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H79">
-        <v>18.01</v>
+        <v>17.33</v>
       </c>
       <c r="I79">
-        <v>15.24</v>
+        <v>14.68</v>
       </c>
       <c r="J79">
-        <v>58.53</v>
+        <v>54.67</v>
       </c>
       <c r="K79">
-        <v>179.05</v>
+        <v>176.46</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M79">
-        <v>11.74</v>
+        <v>14.26</v>
       </c>
       <c r="N79">
-        <v>79.23</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="O79">
-        <v>13.54</v>
+        <v>13.77</v>
       </c>
       <c r="P79">
-        <v>8.220000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q79">
-        <v>203.38</v>
+        <v>137.45</v>
       </c>
       <c r="R79">
-        <v>48.76</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Indeterminate climbing</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Combination 1–2–3</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Slightly curved</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Pale red stripe on green</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Pale yellow</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>All leaves persistent</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Golden yellow</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Cubic</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Lilac</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Lila oscuro con manchas violA!cias</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
+        <v>41.86</v>
       </c>
     </row>
   </sheetData>
